--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_toy-qa-dataset_pos_sample_15_tokens_0.1_temp_direct_answer_raw_table_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_toy-qa-dataset_pos_sample_15_tokens_0.1_temp_direct_answer_raw_table_09-03-1.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in China. The Great Wall of China</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 0.3333), ('.', 1.0), (' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -542,7 +542,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -562,20 +562,20 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 0.3333), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -608,20 +608,20 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 0.3333), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -647,27 +647,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in China. The Great Wall of China</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 0.3333), ('.', 1.0), (' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -693,27 +693,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in China. The Great Wall of China</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 0.3333), ('.', 1.0), (' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -739,27 +739,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in China. The Great Wall of China</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 0.3333), ('.', 1.0), (' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -792,20 +792,20 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 0.3333), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -818,7 +818,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -831,27 +831,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in China. The Great Wall of China</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 0.3333), ('.', 1.0), (' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -877,27 +877,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in the northern part of China. It</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.3333), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China?</t>
+          <t>China. What is the location of the Great Wall of China?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -923,27 +923,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Great Wall of China is located in China. The Great Wall of China</t>
+          <t>The Great Wall of China is located in northern China. It is a series</t>
         </is>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3333333134651184</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9293769598007202</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3662041127681732</v>
+        <v>-0</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 0.3333), ('.', 1.0), (' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0)]</t>
+          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' northern', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' series', 1.0)]</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located?</t>
+          <t>Paris. Where is the Eiffel Tower located?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan?</t>
+          <t>Tokyo. What is the capital city of Japan?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tokyo. The capital city of Japan is Tokyo. Tokyo is the capital city</t>
+          <t>Tokyo. What is the capital city of Japan? Tokyo. What is the</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('.', 1.0), (' The', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
+          <t>[(' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1889,27 +1889,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also very acidic</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F32" t="b">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' very', 0.7773), (' acidic', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1935,27 +1935,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also acidic and</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1113500744104385</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8638653159141541</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6810534000396729</v>
+        <v>-0</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' acidic', 0.2227), (' and', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1981,27 +1981,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also very acidic</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' very', 0.7773), (' acidic', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2027,27 +2027,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also very acidic</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' very', 0.7773), (' acidic', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2073,27 +2073,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is a citrus fruit</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 0.5), (' citrus', 1.0), (' fruit', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also very acidic</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F37" t="b">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' very', 0.7773), (' acidic', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2165,27 +2165,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also acidic and</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F38" t="b">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1113500744104385</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8638653159141541</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6810534000396729</v>
+        <v>-0</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' acidic', 0.2227), (' and', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2211,27 +2211,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is a citrus fruit</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F39" t="b">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 0.5), (' citrus', 1.0), (' fruit', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2257,27 +2257,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is a citrus fruit</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 0.5), (' citrus', 1.0), (' fruit', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon?</t>
+          <t>Sour. How would you describe the taste of a lemon?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2303,27 +2303,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>The taste of a lemon is sour and bitter. It is also very acidic</t>
+          <t>Sour. How would you describe the taste of a lemon? Answer: Sour</t>
         </is>
       </c>
       <c r="F41" t="b">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' is', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' very', 0.7773), (' acidic', 1.0)]</t>
+          <t>[(' Sour', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Sour', 1.0)]</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2365,15 +2365,15 @@
         <v>-0</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2411,15 +2411,15 @@
         <v>-0</v>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2457,15 +2457,15 @@
         <v>-0</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2503,15 +2503,15 @@
         <v>-0</v>
       </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2549,15 +2549,15 @@
         <v>-0</v>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2595,15 +2595,15 @@
         <v>-0</v>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2641,15 +2641,15 @@
         <v>-0</v>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2687,15 +2687,15 @@
         <v>-0</v>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2733,15 +2733,15 @@
         <v>-0</v>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day?</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>A clear day is a day when the sky is clear and the sun is</t>
+          <t>Sunny. What is the best way to describe the weather on a clear day</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2779,15 +2779,15 @@
         <v>-0</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[(' A', 1.0), (' clear', 1.0), (' day', 1.0), (' is', 1.0), (' a', 1.0), (' day', 1.0), (' when', 1.0), (' the', 1.0), (' sky', 1.0), (' is', 1.0), (' clear', 1.0), (' and', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0)]</t>
+          <t>[(' Sunny', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2809,27 +2809,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F52" t="b">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2855,27 +2855,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F53" t="b">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F54" t="b">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2947,27 +2947,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F55" t="b">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2993,27 +2993,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>The feeling of touching velvet is soft and smooth. It is a very pleasant</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F56" t="b">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9117224812507629</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' is', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' pleasant', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3039,27 +3039,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>The feeling of touching velvet is soft and smooth. It is a pleasant sensation</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F57" t="b">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9117224812507629</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6931471824645996</v>
+        <v>-0</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' is', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' pleasant', 0.5), (' sensation', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3085,27 +3085,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F58" t="b">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3177,27 +3177,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F60" t="b">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet?</t>
+          <t>Soft. How would you describe the feeling of touching velvet?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3223,27 +3223,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Velvet is a soft, smooth fabric that feels luxurious and luxurious. It is</t>
+          <t>Soft. How would you describe the feeling of touching velvet? Answer: Soft</t>
         </is>
       </c>
       <c r="F61" t="b">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[(' Velvet', 0.5), (' is', 1.0), (' a', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (' fabric', 1.0), (' that', 1.0), (' feels', 1.0), (' luxurious', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
+          <t>[(' Soft', 1.0), ('.', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Soft', 1.0)]</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States?</t>
+          <t>George Washington. Who was the first president of the United States?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>George Washington. The first president of the United States was George Washington. He</t>
+          <t>George Washington. Who was the first president of the United States? Answer:</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' The', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' was', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' He', 1.0)]</t>
+          <t>[(' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3729,27 +3729,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jane Austen is the author of 'Pride and Prejudice'.</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F72" t="b">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.3944), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'.", 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3775,27 +3775,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jane Austen is the author of 'Pride and Prejudice'.</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F73" t="b">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.3944), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'.", 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3821,28 +3821,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jane Austen
-Who is the author of 'Pride and Prejud</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F74" t="b">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('\n', 0.3944), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -3855,7 +3854,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3868,27 +3867,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jane Austen. Please provide a short, direct answer to the following question</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F75" t="b">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2111267447471619</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0.9015079140663147</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3283647000789642</v>
+        <v>-0</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 0.2111), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3901,7 +3900,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3914,28 +3913,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jane Austen
-Who is the author of 'Pride and Prejud</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F76" t="b">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('\n', 0.3944), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3948,7 +3946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3961,27 +3959,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jane Austen. Please provide a short, direct answer to the following question</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F77" t="b">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2111267447471619</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.9015079140663147</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3283647000789642</v>
+        <v>-0</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 0.2111), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3994,7 +3992,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4007,27 +4005,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jane Austen is the author of 'Pride and Prejudice'.</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F78" t="b">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.3944), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'.", 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -4040,7 +4038,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4053,28 +4051,27 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jane Austen
-Who is the author of 'Pride and Prejud</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F79" t="b">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('\n', 0.3944), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -4087,7 +4084,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4100,28 +4097,27 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jane Austen
-Who is the author of 'Pride and Prejud</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F80" t="b">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('\n', 0.3944), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4134,7 +4130,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'?</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejudice'?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4147,27 +4143,27 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jane Austen is the author of 'Pride and Prejudice'.</t>
+          <t>Jane Austen. Who is the author of 'Pride and Prejud</t>
         </is>
       </c>
       <c r="F81" t="b">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3944366574287415</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9398642778396606</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3669431209564209</v>
+        <v>-0</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.3944), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'.", 1.0)]</t>
+          <t>[(' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4180,7 +4176,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4193,7 +4189,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4213,7 +4209,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4226,7 +4222,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4239,7 +4235,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4259,7 +4255,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4272,7 +4268,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4285,7 +4281,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4305,7 +4301,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -4318,7 +4314,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4331,7 +4327,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4351,7 +4347,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4364,7 +4360,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4377,7 +4373,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4397,7 +4393,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4410,7 +4406,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4423,7 +4419,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4443,7 +4439,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4456,7 +4452,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4469,7 +4465,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4489,7 +4485,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4502,7 +4498,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4515,7 +4511,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4535,7 +4531,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4548,7 +4544,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4561,7 +4557,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4581,7 +4577,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -4594,7 +4590,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa?</t>
+          <t>Leonardo da Vinci. Who painted the Mona Lisa?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4607,7 +4603,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci painted the Mona Lisa. The Mona Lisa is a portrait of</t>
+          <t>Leonardo da Vinci. What is the Mona Lisa? Answer: Leonardo da Vinci</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4627,7 +4623,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' portrait', 1.0), (' of', 1.0)]</t>
+          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0)]</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4640,7 +4636,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4653,31 +4649,31 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like the color blue because it is a</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F92" t="b">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' the', 0.5), (' color', 1.0), (' blue', 1.0), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4686,7 +4682,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4699,31 +4695,31 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like the color blue because it is a</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F93" t="b">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' the', 0.5), (' color', 1.0), (' blue', 1.0), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4732,7 +4728,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4745,31 +4741,31 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like blue because it is a cool color</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F94" t="b">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' blue', 0.5), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0), (' cool', 1.0), (' color', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4778,7 +4774,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4791,31 +4787,31 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like blue because it is a cool color</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F95" t="b">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' blue', 0.5), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0), (' cool', 1.0), (' color', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4824,7 +4820,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4837,31 +4833,31 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>I like the color blue. I like the color blue because it is a</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F96" t="b">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="J96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>[(' I', 0.3486), (' like', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4870,7 +4866,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4883,31 +4879,31 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like blue because it is a cool color</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F97" t="b">
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' blue', 0.5), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0), (' cool', 1.0), (' color', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4916,7 +4912,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4929,31 +4925,31 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>I like the color blue. I like the color blue because it is a</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F98" t="b">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="J98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>[(' I', 0.3486), (' like', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4962,7 +4958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4975,31 +4971,31 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like the color blue because it is a</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F99" t="b">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' the', 0.5), (' color', 1.0), (' blue', 1.0), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -5008,7 +5004,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5021,31 +5017,31 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like the color blue because it is a</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F100" t="b">
         <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' the', 0.5), (' color', 1.0), (' blue', 1.0), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -5054,7 +5050,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>I don't know. What is your favorite color?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5067,31 +5063,31 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>My favorite color is blue. I like blue because it is a cool color</t>
+          <t>I don't know. What is your favorite color? Answer: I don</t>
         </is>
       </c>
       <c r="F101" t="b">
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3256774246692657</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9279384613037109</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6258097887039185</v>
+        <v>-0</v>
       </c>
       <c r="J101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>[(' My', 0.6514), (' favorite', 1.0), (' color', 1.0), (' is', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' blue', 0.5), (' because', 1.0), (' it', 1.0), (' is', 1.0), (' a', 1.0), (' cool', 1.0), (' color', 1.0)]</t>
+          <t>[(' I', 1.0), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' I', 1.0), (' don', 1.0)]</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -5100,7 +5096,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5113,7 +5109,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to be happy. I think that the</t>
+          <t>I think that the meaning of life is to live life to the fullest.</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5133,7 +5129,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' be', 0.5), (' happy', 1.0), ('.', 0.5), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' that', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' life', 0.5), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -5146,7 +5142,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5159,27 +5155,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to live a life that is meaningful.</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F103" t="b">
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.25</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H103" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 0.5), (' a', 0.5), (' life', 1.0), (' that', 1.0), (' is', 1.0), (' meaningful', 1.0), ('.', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -5192,7 +5188,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5205,27 +5201,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to live a life that is meaningful.</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F104" t="b">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0.25</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H104" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J104" t="b">
         <v>0</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 0.5), (' a', 0.5), (' life', 1.0), (' that', 1.0), (' is', 1.0), (' meaningful', 1.0), ('.', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -5238,7 +5234,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5251,7 +5247,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to live it. I think the meaning</t>
+          <t>I think that the meaning of life is to live life to the fullest.</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5271,7 +5267,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 0.5), (' it', 0.5), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' that', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' life', 0.5), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -5284,7 +5280,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5297,27 +5293,27 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to be happy and to be able to</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F106" t="b">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0.125</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H106" t="n">
-        <v>0.8705505728721619</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I106" t="n">
-        <v>1.039720773696899</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J106" t="b">
         <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' be', 0.5), (' happy', 1.0), (' and', 0.5), (' to', 1.0), (' be', 0.5), (' able', 1.0), (' to', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -5330,7 +5326,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5343,27 +5339,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to be happy and to be able to</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F107" t="b">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.125</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H107" t="n">
-        <v>0.8705505728721619</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I107" t="n">
-        <v>1.039720773696899</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J107" t="b">
         <v>0</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' be', 0.5), (' happy', 1.0), (' and', 0.5), (' to', 1.0), (' be', 0.5), (' able', 1.0), (' to', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -5376,7 +5372,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5389,27 +5385,27 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to be happy and to make others happy</t>
+          <t>I think that the meaning of life is to live it. I think that</t>
         </is>
       </c>
       <c r="F108" t="b">
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="H108" t="n">
-        <v>0.8705505728721619</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="I108" t="n">
-        <v>1.039720773696899</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J108" t="b">
         <v>0</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' be', 0.5), (' happy', 1.0), (' and', 0.5), (' to', 1.0), (' make', 0.5), (' others', 1.0), (' happy', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' that', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.5), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' that', 1.0)]</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -5422,7 +5418,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5435,27 +5431,27 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to be happy. I think that the</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F109" t="b">
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.25</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H109" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J109" t="b">
         <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' be', 0.5), (' happy', 1.0), ('.', 0.5), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -5468,7 +5464,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5481,27 +5477,27 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to be happy. I think that the</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F110" t="b">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.25</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H110" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J110" t="b">
         <v>0</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' be', 0.5), (' happy', 1.0), ('.', 0.5), (' I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -5514,7 +5510,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life?</t>
+          <t>It's complicated. What do you think of the meaning of life?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5527,27 +5523,27 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>I think the meaning of life is to live a life that is meaningful.</t>
+          <t>I think the meaning of life is to live it. I think the meaning</t>
         </is>
       </c>
       <c r="F111" t="b">
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.25</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="H111" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9389386773109436</v>
       </c>
       <c r="I111" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="J111" t="b">
         <v>0</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>[(' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 0.5), (' a', 0.5), (' life', 1.0), (' that', 1.0), (' is', 1.0), (' meaningful', 1.0), ('.', 1.0)]</t>
+          <t>[(' I', 1.0), (' think', 1.0), (' the', 0.5), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 0.7773), ('.', 1.0), (' I', 1.0), (' think', 1.0), (' the', 1.0), (' meaning', 1.0)]</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -5560,7 +5556,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5573,31 +5569,31 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>The beginning. Please provide a short, direct answer to the following question:</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F112" t="b">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="J112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' Please', 0.3486), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0), (':', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -5606,7 +5602,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5619,31 +5615,31 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>The beginning. The end is the beginning of the beginning. The beginning is</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F113" t="b">
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0.212131604552269</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>0.901793360710144</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9050460457801819</v>
+        <v>-0</v>
       </c>
       <c r="J113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' The', 0.6514), (' end', 0.5), (' is', 1.0), (' the', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' beginning', 1.0), ('.', 1.0), (' The', 1.0), (' beginning', 1.0), (' is', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5652,7 +5648,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5665,31 +5661,31 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>The end is the beginning of the next thing. The end is the beginning</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F114" t="b">
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1215534284710884</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>0.868929386138916</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7347352504730225</v>
+        <v>-0</v>
       </c>
       <c r="J114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 0.3486), (' is', 1.0), (' the', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.3486), (' thing', 1.0), ('.', 1.0), (' The', 1.0), (' end', 1.0), (' is', 1.0), (' the', 1.0), (' beginning', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -5698,7 +5694,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5711,31 +5707,31 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>The beginning. The beginning of what? The beginning of the next cycle.</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F115" t="b">
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.212131604552269</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>0.901793360710144</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.9050460457801819</v>
+        <v>-0</v>
       </c>
       <c r="J115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' The', 0.6514), (' beginning', 0.5), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), ('.', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5744,7 +5740,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5757,31 +5753,31 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>The beginning. The end is the beginning of the beginning. The beginning is</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F116" t="b">
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0.212131604552269</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>0.901793360710144</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>0.9050460457801819</v>
+        <v>-0</v>
       </c>
       <c r="J116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' The', 0.6514), (' end', 0.5), (' is', 1.0), (' the', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' beginning', 1.0), ('.', 1.0), (' The', 1.0), (' beginning', 1.0), (' is', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -5790,7 +5786,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5803,31 +5799,31 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>The beginning. Please provide a short, direct answer to the following question:</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F117" t="b">
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="J117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' Please', 0.3486), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0), (':', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -5836,7 +5832,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5849,31 +5845,31 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>The beginning. The beginning of what? The beginning of the next cycle.</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F118" t="b">
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>0.212131604552269</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0.901793360710144</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9050460457801819</v>
+        <v>-0</v>
       </c>
       <c r="J118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' The', 0.6514), (' beginning', 0.5), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 1.0), (' cycle', 1.0), ('.', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -5882,7 +5878,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5895,31 +5891,31 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>The beginning. The end is the beginning of the beginning. The beginning is</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F119" t="b">
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.212131604552269</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0.901793360710144</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9050460457801819</v>
+        <v>-0</v>
       </c>
       <c r="J119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' The', 0.6514), (' end', 0.5), (' is', 1.0), (' the', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' beginning', 1.0), ('.', 1.0), (' The', 1.0), (' beginning', 1.0), (' is', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -5928,7 +5924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5941,31 +5937,31 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>The beginning. Please provide a short, direct answer to the following question:</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F120" t="b">
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="J120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' beginning', 0.6514), ('.', 1.0), (' Please', 0.3486), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0), (':', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5974,7 +5970,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>What comes after the end?</t>
+          <t>Nothing. What comes after the end?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5987,31 +5983,31 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The end is the beginning of the next thing. The end is the beginning</t>
+          <t>Nothing. What comes after the end? Answer: Nothing. What comes after</t>
         </is>
       </c>
       <c r="F121" t="b">
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.1215534284710884</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>0.868929386138916</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7347352504730225</v>
+        <v>-0</v>
       </c>
       <c r="J121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 0.3486), (' is', 1.0), (' the', 1.0), (' beginning', 1.0), (' of', 1.0), (' the', 1.0), (' next', 0.3486), (' thing', 1.0), ('.', 1.0), (' The', 1.0), (' end', 1.0), (' is', 1.0), (' the', 1.0), (' beginning', 1.0)]</t>
+          <t>[(' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Nothing', 1.0), ('.', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0)]</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6020,7 +6016,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6033,27 +6029,27 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. They are Africa, Antarctica, Asia,</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F122" t="b">
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J122" t="b">
         <v>1</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -6066,7 +6062,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6079,27 +6075,27 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. They are Africa, Antarctica, Asia,</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F123" t="b">
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -6112,7 +6108,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6125,27 +6121,27 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. They are Africa, Antarctica, Asia,</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F124" t="b">
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -6158,7 +6154,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6171,27 +6167,27 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. The continents are Africa, Antarctica, Asia</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F125" t="b">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' The', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -6204,7 +6200,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6217,27 +6213,27 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. They are Africa, Antarctica, Asia,</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F126" t="b">
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J126" t="b">
         <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -6250,7 +6246,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6263,27 +6259,27 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. The continents are Africa, Antarctica, Asia</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F127" t="b">
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J127" t="b">
         <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' The', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -6296,7 +6292,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6309,27 +6305,27 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. The continents are Africa, Antarctica, Asia</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F128" t="b">
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' The', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -6342,7 +6338,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6355,27 +6351,27 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. The continents are Africa, Antarctica, Asia</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F129" t="b">
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J129" t="b">
         <v>1</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' The', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -6388,7 +6384,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6401,27 +6397,27 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. The continents are Africa, Antarctica, Asia</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F130" t="b">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J130" t="b">
         <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' The', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -6434,7 +6430,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth?</t>
+          <t>Seven. How many continents are there on Earth?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6447,27 +6443,27 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>There are seven continents on Earth. They are Africa, Antarctica, Asia,</t>
+          <t>Seven. How many continents are there on Earth? Answer: Seven. How</t>
         </is>
       </c>
       <c r="F131" t="b">
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J131" t="b">
         <v>1</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>[(' There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[(' Seven', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' continents', 1.0), (' are', 1.0), (' there', 1.0), (' on', 1.0), (' Earth', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Seven', 1.0), ('.', 1.0), (' How', 1.0)]</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -6480,7 +6476,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6493,27 +6489,27 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? The boiling</t>
         </is>
       </c>
       <c r="F132" t="b">
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I132" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J132" t="b">
         <v>1</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' The', 0.5), (' boiling', 1.0)]</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -6526,7 +6522,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6539,27 +6535,27 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? Answer:</t>
         </is>
       </c>
       <c r="F133" t="b">
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I133" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J133" t="b">
         <v>1</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' Answer', 0.5), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -6572,7 +6568,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6585,27 +6581,27 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? Answer:</t>
         </is>
       </c>
       <c r="F134" t="b">
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I134" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' Answer', 0.5), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -6618,7 +6614,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6631,27 +6627,27 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? The boiling</t>
         </is>
       </c>
       <c r="F135" t="b">
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I135" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' The', 0.5), (' boiling', 1.0)]</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -6664,7 +6660,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6677,27 +6673,27 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? Answer:</t>
         </is>
       </c>
       <c r="F136" t="b">
         <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I136" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' Answer', 0.5), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -6710,7 +6706,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6723,27 +6719,27 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? The boiling</t>
         </is>
       </c>
       <c r="F137" t="b">
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I137" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J137" t="b">
         <v>1</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' The', 0.5), (' boiling', 1.0)]</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -6756,7 +6752,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6769,27 +6765,27 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? The boiling</t>
         </is>
       </c>
       <c r="F138" t="b">
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I138" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J138" t="b">
         <v>1</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' The', 0.5), (' boiling', 1.0)]</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -6802,7 +6798,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6815,27 +6811,27 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? Answer:</t>
         </is>
       </c>
       <c r="F139" t="b">
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I139" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' Answer', 0.5), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -6848,7 +6844,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6861,27 +6857,27 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? Answer:</t>
         </is>
       </c>
       <c r="F140" t="b">
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I140" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J140" t="b">
         <v>1</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' Answer', 0.5), (':', 1.0)]</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -6894,7 +6890,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius?</t>
+          <t>100. What is the boiling point of water in Celsius?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6907,27 +6903,27 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>100. What is the boiling point of water in Celsius? The boiling</t>
         </is>
       </c>
       <c r="F141" t="b">
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="I141" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J141" t="b">
         <v>1</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[(' ', 1.0), ('100', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('?', 1.0), (' The', 0.5), (' boiling', 1.0)]</t>
         </is>
       </c>
       <c r="L141" t="n">
@@ -6940,7 +6936,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6953,27 +6949,27 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F142" t="b">
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I142" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J142" t="b">
         <v>1</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -6986,7 +6982,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6999,27 +6995,27 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours.://www.://www.</t>
         </is>
       </c>
       <c r="F143" t="b">
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>0.8900687694549561</v>
       </c>
       <c r="I143" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="J143" t="b">
         <v>1</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3486), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -7032,7 +7028,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7045,27 +7041,27 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F144" t="b">
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I144" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J144" t="b">
         <v>1</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -7078,7 +7074,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7091,27 +7087,27 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours.://www.://www.</t>
         </is>
       </c>
       <c r="F145" t="b">
         <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0.8900687694549561</v>
       </c>
       <c r="I145" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="J145" t="b">
         <v>1</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3486), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -7124,7 +7120,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7137,27 +7133,27 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F146" t="b">
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I146" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J146" t="b">
         <v>1</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -7170,7 +7166,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7183,27 +7179,27 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F147" t="b">
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I147" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J147" t="b">
         <v>1</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -7216,7 +7212,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7229,27 +7225,27 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F148" t="b">
         <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I148" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J148" t="b">
         <v>1</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -7262,7 +7258,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7275,27 +7271,27 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F149" t="b">
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I149" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J149" t="b">
         <v>1</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -7308,7 +7304,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7321,27 +7317,27 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours. 25. How many days are there in a week</t>
         </is>
       </c>
       <c r="F150" t="b">
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I150" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J150" t="b">
         <v>1</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' ', 0.6514), ('25', 1.0), ('.', 1.0), (' How', 1.0), (' many', 1.0), (' days', 1.0), (' are', 1.0), (' there', 1.0), (' in', 1.0), (' a', 1.0), (' week', 1.0)]</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -7354,7 +7350,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>How many hours are there in a day?</t>
+          <t>24. How many hours are there in a day?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7367,27 +7363,27 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>24 hours. Please provide a short, direct answer to the following question</t>
+          <t>24 hours.://www.://www.</t>
         </is>
       </c>
       <c r="F151" t="b">
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="H151" t="n">
-        <v>1</v>
+        <v>0.8900687694549561</v>
       </c>
       <c r="I151" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="J151" t="b">
         <v>1</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' Please', 1.0), (' provide', 1.0), (' a', 1.0), (' short', 1.0), (',', 1.0), (' direct', 1.0), (' answer', 1.0), (' to', 1.0), (' the', 1.0), (' following', 1.0), (' question', 1.0)]</t>
+          <t>[(' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3486), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -7400,7 +7396,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7413,7 +7409,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7433,7 +7429,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -7446,7 +7442,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7459,7 +7455,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7479,7 +7475,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -7492,7 +7488,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7505,7 +7501,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7525,7 +7521,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -7538,7 +7534,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7551,7 +7547,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7571,7 +7567,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -7584,7 +7580,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7597,7 +7593,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7617,7 +7613,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -7630,7 +7626,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7643,7 +7639,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7663,7 +7659,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -7676,7 +7672,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7689,7 +7685,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7709,7 +7705,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -7722,7 +7718,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7735,7 +7731,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7755,7 +7751,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -7768,7 +7764,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7781,7 +7777,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7801,7 +7797,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -7814,7 +7810,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil?</t>
+          <t>Portuguese. What language is primarily spoken in Brazil?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7827,7 +7823,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
+          <t>Portuguese. What language is primarily spoken in Brazil? Answer: Portuguese. What</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7847,7 +7843,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
+          <t>[(' Portuguese', 1.0), ('.', 1.0), (' What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' What', 1.0)]</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -7860,7 +7856,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7873,27 +7869,27 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by the majority of</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F162" t="b">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H162" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J162" t="b">
         <v>1</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773), (' majority', 1.0), (' of', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L162" t="n">
@@ -7906,7 +7902,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7919,27 +7915,27 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by 95%</t>
+          <t>German. German is the official language of Germany. It is spoken by</t>
         </is>
       </c>
       <c r="F163" t="b">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="H163" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9047210812568665</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="J163" t="b">
         <v>1</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 0.2227), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 0.2227)]</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -7952,7 +7948,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7965,27 +7961,27 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. German is the most widely spoken language</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F164" t="b">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.5</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H164" t="n">
-        <v>0.9548416137695312</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J164" t="b">
         <v>1</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' German', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L164" t="n">
@@ -7998,7 +7994,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8011,27 +8007,27 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by the majority of</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F165" t="b">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H165" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J165" t="b">
         <v>1</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773), (' majority', 1.0), (' of', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -8044,7 +8040,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8057,27 +8053,27 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by 95%</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F166" t="b">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H166" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I166" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J166" t="b">
         <v>1</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 0.2227), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -8090,7 +8086,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8103,27 +8099,27 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by the majority of</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F167" t="b">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H167" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J167" t="b">
         <v>1</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773), (' majority', 1.0), (' of', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -8136,7 +8132,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8149,27 +8145,27 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by the majority of</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F168" t="b">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H168" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J168" t="b">
         <v>1</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773), (' majority', 1.0), (' of', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L168" t="n">
@@ -8182,7 +8178,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8195,27 +8191,27 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. German is the most widely spoken language</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F169" t="b">
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>0.5</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H169" t="n">
-        <v>0.9548416137695312</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J169" t="b">
         <v>1</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' German', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -8228,7 +8224,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8241,27 +8237,27 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. It is spoken by the majority of</t>
+          <t>German. German is the official language of Germany. It is spoken by the</t>
         </is>
       </c>
       <c r="F170" t="b">
         <v>1</v>
       </c>
       <c r="G170" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="H170" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="I170" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="J170" t="b">
         <v>1</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773), (' majority', 1.0), (' of', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' the', 0.7773)]</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -8274,7 +8270,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany?</t>
+          <t>German. Which language is spoken in Germany?</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8287,27 +8283,27 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>German is the official language of Germany. German is the most widely spoken language</t>
+          <t>German. German is the official language of Germany. It is spoken by</t>
         </is>
       </c>
       <c r="F171" t="b">
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0.5</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="H171" t="n">
-        <v>0.9548416137695312</v>
+        <v>0.9047210812568665</v>
       </c>
       <c r="I171" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="J171" t="b">
         <v>1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' German', 0.5), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' German', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 0.2227)]</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -8320,7 +8316,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8333,27 +8329,27 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. Mandarin is the official language of China</t>
         </is>
       </c>
       <c r="F172" t="b">
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I172" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J172" t="b">
         <v>1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' Mandarin', 0.6514), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -8366,7 +8362,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8379,27 +8375,27 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. Mandarin is the official language of China</t>
         </is>
       </c>
       <c r="F173" t="b">
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H173" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I173" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J173" t="b">
         <v>1</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' Mandarin', 0.6514), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -8412,7 +8408,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8425,27 +8421,27 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. It is spoken by over 1</t>
         </is>
       </c>
       <c r="F174" t="b">
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>0.2710018157958984</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>0.9166386127471924</v>
       </c>
       <c r="I174" t="n">
-        <v>-0</v>
+        <v>0.5631920099258423</v>
       </c>
       <c r="J174" t="b">
         <v>1</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.3486), (' is', 1.0), (' spoken', 0.7773), (' by', 1.0), (' over', 1.0), (' ', 1.0), ('1', 1.0)]</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -8458,7 +8454,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8471,27 +8467,27 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. Mandarin is the official language of China</t>
         </is>
       </c>
       <c r="F175" t="b">
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I175" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J175" t="b">
         <v>1</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' Mandarin', 0.6514), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -8504,7 +8500,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8517,27 +8513,27 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. Mandarin is the official language of China</t>
         </is>
       </c>
       <c r="F176" t="b">
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H176" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I176" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J176" t="b">
         <v>1</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' Mandarin', 0.6514), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -8550,7 +8546,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8563,27 +8559,27 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. Mandarin is the official language of China</t>
         </is>
       </c>
       <c r="F177" t="b">
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I177" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J177" t="b">
         <v>1</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' Mandarin', 0.6514), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -8596,7 +8592,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8609,27 +8605,27 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. Mandarin is the official language of China</t>
         </is>
       </c>
       <c r="F178" t="b">
         <v>1</v>
       </c>
       <c r="G178" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="H178" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="I178" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="J178" t="b">
         <v>1</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' Mandarin', 0.6514), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0)]</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -8642,7 +8638,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8655,27 +8651,27 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. It is spoken by over 1</t>
         </is>
       </c>
       <c r="F179" t="b">
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>1</v>
+        <v>0.2710018157958984</v>
       </c>
       <c r="H179" t="n">
-        <v>1</v>
+        <v>0.9166386127471924</v>
       </c>
       <c r="I179" t="n">
-        <v>-0</v>
+        <v>0.5631920099258423</v>
       </c>
       <c r="J179" t="b">
         <v>1</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.3486), (' is', 1.0), (' spoken', 0.7773), (' by', 1.0), (' over', 1.0), (' ', 1.0), ('1', 1.0)]</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -8688,7 +8684,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8701,27 +8697,27 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. It is spoken by over 1</t>
         </is>
       </c>
       <c r="F180" t="b">
         <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>0.2710018157958984</v>
       </c>
       <c r="H180" t="n">
-        <v>1</v>
+        <v>0.9166386127471924</v>
       </c>
       <c r="I180" t="n">
-        <v>-0</v>
+        <v>0.5631920099258423</v>
       </c>
       <c r="J180" t="b">
         <v>1</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.3486), (' is', 1.0), (' spoken', 0.7773), (' by', 1.0), (' over', 1.0), (' ', 1.0), ('1', 1.0)]</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -8734,7 +8730,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>What is the official language of China?</t>
+          <t>Mandarin. What is the official language of China?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8747,27 +8743,27 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>The official language of China is Mandarin. Mandarin is the most widely spoken language</t>
+          <t>Mandarin is the official language of China. It is spoken by over 1</t>
         </is>
       </c>
       <c r="F181" t="b">
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>1</v>
+        <v>0.2710018157958984</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>0.9166386127471924</v>
       </c>
       <c r="I181" t="n">
-        <v>-0</v>
+        <v>0.5631920099258423</v>
       </c>
       <c r="J181" t="b">
         <v>1</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0)]</t>
+          <t>[(' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 0.3486), (' is', 1.0), (' spoken', 0.7773), (' by', 1.0), (' over', 1.0), (' ', 1.0), ('1', 1.0)]</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -8780,7 +8776,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8793,7 +8789,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F182" t="b">
@@ -8813,7 +8809,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -8826,7 +8822,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8839,7 +8835,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8859,7 +8855,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L183" t="n">
@@ -8872,7 +8868,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8885,7 +8881,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8905,7 +8901,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L184" t="n">
@@ -8918,7 +8914,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8931,7 +8927,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8951,7 +8947,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -8964,7 +8960,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8977,7 +8973,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8997,7 +8993,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L186" t="n">
@@ -9010,7 +9006,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -9023,7 +9019,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -9043,7 +9039,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -9056,7 +9052,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -9069,7 +9065,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -9089,7 +9085,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -9102,7 +9098,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9115,7 +9111,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -9135,7 +9131,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -9148,7 +9144,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9161,7 +9157,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F190" t="b">
@@ -9181,7 +9177,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -9194,7 +9190,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone?</t>
+          <t>Apple. Which company developed the iPhone?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9207,7 +9203,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Apple Inc. developed the iPhone. The iPhone is a smartphone that was developed</t>
+          <t>Apple. Which company developed the iPhone? Apple. Which company developed the iPhone</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -9227,7 +9223,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' that', 1.0), (' was', 1.0), (' developed', 1.0)]</t>
+          <t>[(' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?', 1.0), (' Apple', 1.0), ('.', 1.0), (' Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0)]</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -9240,7 +9236,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9253,8 +9249,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -9274,7 +9269,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -9287,7 +9282,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9300,8 +9295,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -9321,7 +9315,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L193" t="n">
@@ -9334,7 +9328,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9347,8 +9341,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -9368,7 +9361,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -9381,7 +9374,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9394,8 +9387,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9415,7 +9407,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L195" t="n">
@@ -9428,7 +9420,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9441,8 +9433,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F196" t="b">
@@ -9462,7 +9453,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L196" t="n">
@@ -9475,7 +9466,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9488,8 +9479,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -9509,7 +9499,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L197" t="n">
@@ -9522,7 +9512,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9535,8 +9525,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9556,7 +9545,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L198" t="n">
@@ -9569,7 +9558,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9582,8 +9571,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9603,7 +9591,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L199" t="n">
@@ -9616,7 +9604,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9629,8 +9617,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F200" t="b">
@@ -9650,7 +9637,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L200" t="n">
@@ -9663,7 +9650,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos?</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9676,8 +9663,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Amazon.com
-What is the name of the online retailer founded by Jeff Be</t>
+          <t>Amazon. What is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9697,7 +9683,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0)]</t>
+          <t>[(' Amazon', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="L201" t="n">
@@ -9710,7 +9696,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9723,7 +9709,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9743,7 +9729,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L202" t="n">
@@ -9756,7 +9742,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9769,7 +9755,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9789,7 +9775,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L203" t="n">
@@ -9802,7 +9788,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9815,7 +9801,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9835,7 +9821,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L204" t="n">
@@ -9848,7 +9834,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9861,7 +9847,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9881,7 +9867,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L205" t="n">
@@ -9894,7 +9880,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9907,7 +9893,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9927,7 +9913,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L206" t="n">
@@ -9940,7 +9926,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9953,7 +9939,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9973,7 +9959,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L207" t="n">
@@ -9986,7 +9972,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9999,7 +9985,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -10019,7 +10005,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L208" t="n">
@@ -10032,7 +10018,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10045,7 +10031,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -10065,7 +10051,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L209" t="n">
@@ -10078,7 +10064,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -10091,7 +10077,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F210" t="b">
@@ -10111,7 +10097,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L210" t="n">
@@ -10124,7 +10110,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine?</t>
+          <t>Google. Which company is known for its search engine?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10137,7 +10123,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Google is known for its search engine. Google is a multinational technology company that</t>
+          <t>Google is a multinational technology company that specializes in Internet-related services and products,</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -10157,7 +10143,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('.', 1.0), (' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0)]</t>
+          <t>[(' Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L211" t="n">
